--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92566945717</v>
+        <v>46157.93095585751</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93095585751</v>
+        <v>46157.93171137914</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93171137914</v>
+        <v>46157.93398777112</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93398777112</v>
+        <v>46157.93716515618</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93716515618</v>
+        <v>46158.28215143464</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28215143464</v>
+        <v>46158.29676641116</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29676641116</v>
+        <v>46158.29813217135</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29813217135</v>
+        <v>46158.33386087684</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33386087684</v>
+        <v>46158.36855860683</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36855860683</v>
+        <v>46158.37286582078</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
